--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.54410193171095</v>
+        <v>8.538416563903029</v>
       </c>
       <c r="D2" t="n">
-        <v>51.12528992960397</v>
+        <v>8.307859613560645</v>
       </c>
       <c r="E2" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F2" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.06062636048283</v>
+        <v>8.622351783578459</v>
       </c>
       <c r="D3" t="n">
-        <v>50.16930083694501</v>
+        <v>8.152511386003564</v>
       </c>
       <c r="E3" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F3" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.52463100386848</v>
+        <v>7.885252538128628</v>
       </c>
       <c r="D4" t="n">
-        <v>45.63627577432636</v>
+        <v>7.415894813328033</v>
       </c>
       <c r="E4" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F4" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.03191377251127</v>
+        <v>6.505185988033082</v>
       </c>
       <c r="D5" t="n">
-        <v>37.14011803690119</v>
+        <v>6.035269180996443</v>
       </c>
       <c r="E5" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F5" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.72780241810661</v>
+        <v>10.68076789294232</v>
       </c>
       <c r="D6" t="n">
-        <v>64.34477445760456</v>
+        <v>10.45602584936074</v>
       </c>
       <c r="E6" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F6" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.15496863955136</v>
+        <v>5.225182403927096</v>
       </c>
       <c r="D7" t="n">
-        <v>32.46659008156515</v>
+        <v>5.275820888254337</v>
       </c>
       <c r="E7" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F7" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.38244305386524</v>
+        <v>9.974646996253101</v>
       </c>
       <c r="D8" t="n">
-        <v>58.96367466995998</v>
+        <v>9.581597133868497</v>
       </c>
       <c r="E8" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F8" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.44226436470149</v>
+        <v>2.671867959263992</v>
       </c>
       <c r="D9" t="n">
-        <v>13.56925333395987</v>
+        <v>2.205003666768479</v>
       </c>
       <c r="E9" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F9" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.76667136301622</v>
+        <v>6.787084096490136</v>
       </c>
       <c r="D10" t="n">
-        <v>39.70462882016989</v>
+        <v>6.452002183277607</v>
       </c>
       <c r="E10" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F10" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.02549697302165</v>
+        <v>3.416643258116019</v>
       </c>
       <c r="D11" t="n">
-        <v>16.45824435732229</v>
+        <v>2.674464708064872</v>
       </c>
       <c r="E11" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F11" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.71637467545951</v>
+        <v>9.216410884762171</v>
       </c>
       <c r="D12" t="n">
-        <v>29.41506973936558</v>
+        <v>4.779948832646907</v>
       </c>
       <c r="E12" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F12" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.45108231932383</v>
+        <v>10.63580087689012</v>
       </c>
       <c r="D13" t="n">
-        <v>13.79965032529536</v>
+        <v>2.242443177860496</v>
       </c>
       <c r="E13" t="n">
-        <v>15.70558664091288</v>
+        <v>2.552157829148343</v>
       </c>
       <c r="F13" t="n">
-        <v>16.49715590554641</v>
+        <v>2.680787834651291</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
